--- a/WNBA_Elo/Results/WNBA_2026_Results.xlsx
+++ b/WNBA_Elo/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\WNBA_Elo\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC7BD83-3F53-4E86-8B4E-C197CBCFF7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C02136-594A-418F-8E8C-C2ED3835E287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -14156,6 +14156,15 @@
       <c r="G426" t="s">
         <v>24</v>
       </c>
+      <c r="H426">
+        <v>89</v>
+      </c>
+      <c r="I426">
+        <v>98</v>
+      </c>
+      <c r="J426">
+        <v>0</v>
+      </c>
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
@@ -14179,6 +14188,15 @@
       <c r="G427" t="s">
         <v>25</v>
       </c>
+      <c r="H427">
+        <v>98</v>
+      </c>
+      <c r="I427">
+        <v>89</v>
+      </c>
+      <c r="J427">
+        <v>0</v>
+      </c>
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
@@ -14202,6 +14220,15 @@
       <c r="G428" t="s">
         <v>24</v>
       </c>
+      <c r="H428">
+        <v>112</v>
+      </c>
+      <c r="I428">
+        <v>98</v>
+      </c>
+      <c r="J428">
+        <v>0</v>
+      </c>
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
@@ -14225,6 +14252,15 @@
       <c r="G429" t="s">
         <v>25</v>
       </c>
+      <c r="H429">
+        <v>98</v>
+      </c>
+      <c r="I429">
+        <v>112</v>
+      </c>
+      <c r="J429">
+        <v>0</v>
+      </c>
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
@@ -14248,6 +14284,15 @@
       <c r="G430" t="s">
         <v>24</v>
       </c>
+      <c r="H430">
+        <v>75</v>
+      </c>
+      <c r="I430">
+        <v>81</v>
+      </c>
+      <c r="J430">
+        <v>0</v>
+      </c>
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
@@ -14270,6 +14315,15 @@
       </c>
       <c r="G431" t="s">
         <v>25</v>
+      </c>
+      <c r="H431">
+        <v>81</v>
+      </c>
+      <c r="I431">
+        <v>75</v>
+      </c>
+      <c r="J431">
+        <v>0</v>
       </c>
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.35">
